--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA146"/>
+  <dimension ref="A1:AA149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16564,6 +16564,357 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Winseler</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Wiltz</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>19 Route de Bastogne</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delhaize.lu</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>sstroobants@delhaize.lu</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>+352 32 26 20 1634</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>B97993</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delhaize-luxembourg-sa/</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delhaize.pommerloch/</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delhaize_lu/</t>
+        </is>
+      </c>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delhaizeluxembourg8193/</t>
+        </is>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>Thibault Thiel</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sourcing</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thibault-thiel-7983a011b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Winseler</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Wiltz</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>19 Route de Bastogne</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delhaize.lu</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>sstroobants@delhaize.lu</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>+352 32 26 20 1634</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>B97993</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delhaize-luxembourg-sa/</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delhaize.pommerloch/</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delhaize_lu/</t>
+        </is>
+      </c>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delhaizeluxembourg8193/</t>
+        </is>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>Safira Stroobants</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/safira-stroobants-656b90128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Winseler</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Wiltz</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>19 Route de Bastogne</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delhaize.lu</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>sstroobants@delhaize.lu</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>+352 32 26 20 1634</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>B97993</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delhaize-luxembourg-sa/</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delhaize.pommerloch/</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delhaize_lu/</t>
+        </is>
+      </c>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delhaizeluxembourg8193/</t>
+        </is>
+      </c>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>Isaline Carlier</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Category Manager</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/isaline-carlier09/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA149"/>
+  <dimension ref="A1:AA152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16915,6 +16915,357 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Winseler</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Wiltz</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>19 Route de Bastogne</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delhaize.lu</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>sstroobants@delhaize.lu</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>+352 32 26 20 1634</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>B97993</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delhaize-luxembourg-sa/</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delhaize.pommerloch/</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delhaize_lu/</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delhaizeluxembourg8193/</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>Thibault Thiel</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Sourcing</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thibault-thiel-7983a011b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Winseler</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Wiltz</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>19 Route de Bastogne</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delhaize.lu</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>sstroobants@delhaize.lu</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>+352 32 26 20 1634</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>B97993</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delhaize-luxembourg-sa/</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delhaize.pommerloch/</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delhaize_lu/</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delhaizeluxembourg8193/</t>
+        </is>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>Safira Stroobants</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/safira-stroobants-656b90128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Delhaize Luxembourg S.a.</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Winseler</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Wiltz</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>19 Route de Bastogne</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delhaize.lu</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>sstroobants@delhaize.lu</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>+352 32 26 20 1634</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>B97993</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delhaize-luxembourg-sa/</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delhaize.pommerloch/</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delhaize_lu/</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delhaizeluxembourg8193/</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>Isaline Carlier</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Category Manager</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/isaline-carlier09/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA152"/>
+  <dimension ref="A1:AA155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17266,6 +17266,289 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Vinsroumains</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Vinsroumains</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>9495</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Koerich</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>22 Rue de l'Industrie</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>8399</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinsroumains.com</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>contact@vinsroumains.com</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr"/>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr"/>
+      <c r="R153" s="2" t="inlineStr"/>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Romanian-wines-in-Luxembourg-175102829991081/</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>Georges Lazu</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vins-roumain-georges-lazu-b55920b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Spirilux Sàrl</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Spirilux Sàrl</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>43809</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Käerjeng</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>54 Zone Op Zaemer</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atelierdubarman.com</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>info@atelierdubarman.com</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr"/>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>B151242</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/atelier-du-barman</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/atelierdubarman/</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/atelierdubarman</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>Benoit Tintinger</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benoit-tintinger-b18a064a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Tendance Vins S.à.r.l.</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Tendance Vins S.à.r.l.</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>9505</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Kehlen</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>22 Zone Industrielle</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>8287</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>http://tendancevins.lu</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>fabian.moris@tendancevins.lu</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr"/>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>B107010</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr"/>
+      <c r="S155" s="2" t="inlineStr"/>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tendance_vins</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>Fabian Moris</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA155"/>
+  <dimension ref="A1:AA157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17549,6 +17549,224 @@
       <c r="Z155" s="2" t="inlineStr"/>
       <c r="AA155" s="2" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Amuse-bouche S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Amuse-bouche S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>122090</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Sanem</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Rue De Differdange 195-197</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amuse-bouche.lu</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>info@amuse-bouche.lu</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 59 04 13</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>B195685</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amuse-bouche-vins-epicerie-fine/</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/amusebouchezolwer</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amusebouche_soleuvre/</t>
+        </is>
+      </c>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>Camille Ney</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/camille-ney-630a6a9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Amuse-bouche S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Amuse-bouche S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>122090</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Sanem</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Rue De Differdange 195-197</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amuse-bouche.lu</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>info@amuse-bouche.lu</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 59 04 13</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>B195685</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amuse-bouche-vins-epicerie-fine/</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/amusebouchezolwer</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amusebouche_soleuvre/</t>
+        </is>
+      </c>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>Romain Danel</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/romain-danel-9499a161/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17767,6 +17767,1367 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Hobuch Wine &amp; Spirits Sarl</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Hobuch Wine &amp; Spirits Sarl</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>50034</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Hesperange</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>237 Route de Thionville</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>5885</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://hobuch.eu</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>info@hobuch.eu</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 35 21 34</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>B136874</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hobuch-international-s%C3%A0rl/</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sohila.hobuchdelux</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hobuchwineandspirits</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Kintziger</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Manager</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarah-kintziger-6a613847/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Hobuch Wine &amp; Spirits Sarl</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Hobuch Wine &amp; Spirits Sarl</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>50034</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Hesperange</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>237 Route de Thionville</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>5885</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://hobuch.eu</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>info@hobuch.eu</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 35 21 34</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>B136874</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hobuch-international-s%C3%A0rl/</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sohila.hobuchdelux</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hobuchwineandspirits</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>Erick Viloria</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erick-viloria-a8b7aa91/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Vinothèque Le Chai</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Vinothèque Le Chai</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>26268</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Hesperange</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>28 Rue de Bettembourg</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://fr.lechai.lu</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>vinotheque.hesperange@munhowen.lu</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 36 10 52</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinothequelechai/</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/munhowen_le_chai</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>Sylvain Denis</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sylvain-denis-99275915a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Le Vin Passionnément</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Le Vin Passionnément</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>23988</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Mamer</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>55 Route d'Arlon</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://levinpassionnement.lu</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>bourtembourg.philippe@gmail.com</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 31 14 20</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>B180547</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr"/>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Bourtembourg</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>42315</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Bertrange</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>1 Route d'Arlon</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://la-cave-des-sommeliers.com</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>info@lacavedessommeliers.lu</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 10 89 1023</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>B90316</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedessommeliers</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdTTjNEoiYafY2vLI8uWaJQ</t>
+        </is>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>Pascal Carre</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier/ Founder</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pascal-carr%C3%A9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>42315</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Bertrange</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>1 Route d'Arlon</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://la-cave-des-sommeliers.com</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>info@lacavedessommeliers.lu</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 10 89 1023</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>B90316</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedessommeliers</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdTTjNEoiYafY2vLI8uWaJQ</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>Samir Chalbi</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>Management Assistant</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samir-chalbi-494a051b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>42315</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Bertrange</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>1 Route d'Arlon</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://la-cave-des-sommeliers.com</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>info@lacavedessommeliers.lu</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 10 89 1023</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>B90316</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedessommeliers</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdTTjNEoiYafY2vLI8uWaJQ</t>
+        </is>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>Laura Scala</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manager </t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/laura-scala/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>La Cave Des Sommeliers Sprl</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>42315</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Bertrange</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>1 Route d'Arlon</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://la-cave-des-sommeliers.com</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>info@lacavedessommeliers.lu</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 10 89 1023</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>B90316</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedessommeliers</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacavedessommeliers/</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdTTjNEoiYafY2vLI8uWaJQ</t>
+        </is>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>Julien Franzetti</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/julien-franzetti-9567a0bb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Winebrations S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Winebrations S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>53833</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Stadbriedemes</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Réimech</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>20 Kerwech</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>5427</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>http://winebrations.com</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>info@winebrations.com</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>B205805</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winebrations</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr"/>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Taste Of Africa Sàrl</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Taste Of Africa Sàrl</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>9504</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Contern</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>49 Rue de Contern</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://taste-of-africa.eu</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>info@taste-of-africa.eu</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 35 25 56</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>B107919</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr"/>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>Nadine Pyter</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nadine-pyter-22334a19/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Maxi-vins - Vino Select S.a.</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Maxi-vins - Vino Select S.a.</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>28535</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Strassen</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>148 Route d'Arlon</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.maxivins.lu</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>info@maxivins.lu</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 31 15 52</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>B89565</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxivins-luxembourg/</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maxivins.strassen.500/</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>Julien Houberdon</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/julien-houberdon-aa445869/?originalSubdomain=lu</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Eurovin S.a.</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Eurovin S.a.</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>9509</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>1 Rue Frederic Guillaume Raiffeisen</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://vinissimo.lu</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>info@vinissimo.lu</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>+352 52 52 10 500</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>B71214</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinissimoluxembourg/</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinissimoluxembourg/</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinissimo.lu</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Feduzi</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>Wine Cellar Manager</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucas-feduzi-52565661/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Eurovin S.a.</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Eurovin S.a.</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>9509</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>1 Rue Frederic Guillaume Raiffeisen</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://vinissimo.lu</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>info@vinissimo.lu</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>+352 52 52 10 500</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>B71214</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinissimoluxembourg/</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinissimoluxembourg/</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinissimo.lu</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Guillaume Quentel</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/guillaume-quentel-120419b9/?originalSubdomain=lu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA170"/>
+  <dimension ref="A1:AA174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19128,6 +19128,350 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>38736</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>58 Rue Louis Pasteur</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>http://coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>contact@coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 56 79 44</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>B152575</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr"/>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr"/>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>Benoit Bruant</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benoit-bruant-9b5a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr"/>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>Isabelle Bruant</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/isabelle-bruant-7b3b9111b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Contern</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>6 Rue Bélair</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>http://bio-vinis.lu</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>biovinis@pt.lu</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>+352 27 69 47 94</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>B144254</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Biovinis-1453178424982754/</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr"/>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA174"/>
+  <dimension ref="A1:AA179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19472,6 +19472,427 @@
       <c r="Z174" s="2" t="inlineStr"/>
       <c r="AA174" s="2" t="inlineStr"/>
     </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>53780</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>LUXEMBOURG</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>28 Route de Capellen</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>8279</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://bonimores.lu</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>contact@bonimores.lu</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 00 89 93</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr"/>
+      <c r="R175" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr"/>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonimoresbeveragesmore/</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr"/>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>38736</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>58 Rue Louis Pasteur</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>http://coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>contact@coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 56 79 44</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>B152575</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr"/>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr"/>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr"/>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>Benoit Bruant</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benoit-bruant-9b5a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr"/>
+      <c r="S178" s="2" t="inlineStr"/>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>Isabelle Bruant</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/isabelle-bruant-7b3b9111b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Contern</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>6 Rue Bélair</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>http://bio-vinis.lu</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>biovinis@pt.lu</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>+352 27 69 47 94</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>B144254</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr"/>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Biovinis-1453178424982754/</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr"/>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA179"/>
+  <dimension ref="A1:AA184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19893,6 +19893,427 @@
       <c r="Z179" s="2" t="inlineStr"/>
       <c r="AA179" s="2" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>53780</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>LUXEMBOURG</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>28 Route de Capellen</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>8279</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://bonimores.lu</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>contact@bonimores.lu</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 00 89 93</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr"/>
+      <c r="S180" s="2" t="inlineStr"/>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonimoresbeveragesmore/</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr"/>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>38736</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>58 Rue Louis Pasteur</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>http://coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>contact@coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 56 79 44</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>B152575</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr"/>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr"/>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr"/>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>Benoit Bruant</t>
+        </is>
+      </c>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benoit-bruant-9b5a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr"/>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr"/>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>Isabelle Bruant</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/isabelle-bruant-7b3b9111b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Contern</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>6 Rue Bélair</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>http://bio-vinis.lu</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>biovinis@pt.lu</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>+352 27 69 47 94</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>B144254</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr"/>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Biovinis-1453178424982754/</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
+      <c r="X184" s="2" t="inlineStr"/>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA184"/>
+  <dimension ref="A1:AA189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20314,6 +20314,427 @@
       <c r="Z184" s="2" t="inlineStr"/>
       <c r="AA184" s="2" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>53780</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>LUXEMBOURG</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>28 Route de Capellen</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>8279</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://bonimores.lu</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>contact@bonimores.lu</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 00 89 93</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr"/>
+      <c r="R185" s="2" t="inlineStr"/>
+      <c r="S185" s="2" t="inlineStr"/>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonimoresbeveragesmore/</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr"/>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>38736</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>58 Rue Louis Pasteur</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>http://coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>contact@coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 56 79 44</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>B152575</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr"/>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr"/>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr"/>
+      <c r="Q187" s="2" t="inlineStr"/>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr"/>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr">
+        <is>
+          <t>Benoit Bruant</t>
+        </is>
+      </c>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benoit-bruant-9b5a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr"/>
+      <c r="S188" s="2" t="inlineStr"/>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr">
+        <is>
+          <t>Isabelle Bruant</t>
+        </is>
+      </c>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/isabelle-bruant-7b3b9111b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Contern</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>6 Rue Bélair</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>http://bio-vinis.lu</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>biovinis@pt.lu</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>+352 27 69 47 94</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>B144254</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr"/>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Biovinis-1453178424982754/</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr"/>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Luxembourg.xlsx
+++ b/BWI/bestwine_output/bestwine_Luxembourg.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA189"/>
+  <dimension ref="A1:AA194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20735,6 +20735,427 @@
       <c r="Z189" s="2" t="inlineStr"/>
       <c r="AA189" s="2" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Bonimores</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>53780</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>LUXEMBOURG</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Capellen</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>28 Route de Capellen</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>8279</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://bonimores.lu</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>contact@bonimores.lu</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 00 89 93</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr"/>
+      <c r="R190" s="2" t="inlineStr"/>
+      <c r="S190" s="2" t="inlineStr"/>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonimoresbeveragesmore/</t>
+        </is>
+      </c>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr"/>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Cote &amp; Vins S.àr.l.</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>38736</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Esch-sur-Alzette</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>58 Rue Louis Pasteur</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>http://coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>contact@coteetvins.fr</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 56 79 44</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>B152575</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr"/>
+      <c r="S191" s="2" t="inlineStr"/>
+      <c r="T191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr"/>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr"/>
+      <c r="S192" s="2" t="inlineStr"/>
+      <c r="T192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>Benoit Bruant</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benoit-bruant-9b5a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg Drinks S.à.r.l</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>54127</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Rambrouch</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Diekirch, Redange</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>14 Route de Bigonville</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>info@luxembourg-drinks.lu</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>+352 26 61 78 18</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr"/>
+      <c r="R193" s="2" t="inlineStr"/>
+      <c r="S193" s="2" t="inlineStr"/>
+      <c r="T193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>Isabelle Bruant</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/isabelle-bruant-7b3b9111b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Raifrench S.à R.l.</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Contern</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>6 Rue Bélair</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>http://bio-vinis.lu</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>biovinis@pt.lu</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>+352 27 69 47 94</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>B144254</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr"/>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Biovinis-1453178424982754/</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
+      <c r="X194" s="2" t="inlineStr"/>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
